--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\DataTables\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FB38CD-3DAD-438A-A2E5-1A8C2C57DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA93F4CE-2546-4741-9458-3A969B76B6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="2910" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="30">
   <si>
     <t>StoryID</t>
   </si>
@@ -71,10 +82,6 @@
   </si>
   <si>
     <t>李东壁</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>明嘉靖十一年，蕲州州衙放榜处</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -121,17 +128,14 @@
   </si>
   <si>
     <r>
-      <t>考了三次童</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>试</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这说</t>
     </r>
     <r>
       <rPr>
@@ -141,17 +145,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>都没中，看来我不是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>读书</t>
+      <t>的是什么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
     </r>
     <r>
       <rPr>
@@ -161,30 +165,59 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的材料啊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>爹</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这说</t>
+      <t>，你看隔壁村那个老范</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PortraitPath</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/li_shi_zhen.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/li_yan_wen.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>明嘉靖十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>九</t>
     </r>
     <r>
       <rPr>
@@ -194,17 +227,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的是什么</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话</t>
+      <t>年，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武昌府</t>
     </r>
     <r>
       <rPr>
@@ -214,43 +247,23 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，你看隔壁村那个老范</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>我看我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
+      <t>放榜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>考了三次</t>
     </r>
     <r>
       <rPr>
@@ -260,14 +273,14 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>是跟您学医吧，科</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
+      <t>都没中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>举</t>
@@ -280,34 +293,180 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>，看来我不是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的材料啊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爹</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>我看我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>是跟您学医吧，科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>八股什么的，</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实在是学不来…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>可我真心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜欢研究那些药材方子，考证典籍。行医治病才是儿子此生志愿。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢。东壁呀，你若真的想从医，今日起便随为父从《内经》，《本草》学起吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
         <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>太难了</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PortraitPath</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/li_shi_zhen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/li_yan_wen.png</t>
+        <charset val="128"/>
+      </rPr>
+      <t>壁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>十四岁考中秀才，可之后九年三次乡试落榜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，本就无心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>科举的李东壁便下定决心开始随父亲学医。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -319,7 +478,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -333,7 +492,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -455,7 +614,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -736,14 +895,14 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.46484375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="86.73046875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="139.75" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -767,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -790,7 +949,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -813,10 +972,10 @@
         <v>11</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,10 +998,10 @@
         <v>11</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -859,16 +1018,16 @@
         <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -891,10 +1050,10 @@
         <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -917,10 +1076,10 @@
         <v>11</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -937,16 +1096,16 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -969,10 +1128,10 @@
         <v>11</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -989,47 +1148,89 @@
         <v>6</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H10" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="7"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="10"/>
+      <c r="H12" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="10"/>
+      <c r="H13" s="10" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="8"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\DataTables\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA93F4CE-2546-4741-9458-3A969B76B6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F38383D-8FCB-4E25-9A42-E632A8479F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -576,12 +576,6 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -611,6 +605,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -895,362 +895,362 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="139.75" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="139.75" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="3" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>12</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="10" t="s">
+      <c r="E13" s="3"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="10"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="10"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F38383D-8FCB-4E25-9A42-E632A8479F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E328F8-72C8-482B-9A1C-47BAFF00C5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -198,14 +198,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/li_shi_zhen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/li_yan_wen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>明嘉靖十</t>
     </r>
@@ -467,6 +459,14 @@
       </rPr>
       <t>科举的李东壁便下定决心开始随父亲学医。</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -533,7 +533,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,6 +543,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -611,6 +617,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -901,7 +928,7 @@
     <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="139.75" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -949,7 +976,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -972,7 +999,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>14</v>
@@ -998,35 +1025,35 @@
         <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:8" s="18" customFormat="1">
+      <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="15">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1050,7 +1077,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>18</v>
@@ -1076,35 +1103,35 @@
         <v>11</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="18" customFormat="1">
+      <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="15">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1128,35 +1155,35 @@
         <v>11</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="18" customFormat="1">
+      <c r="A10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="15">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1180,36 +1207,36 @@
         <v>11</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="18" customFormat="1">
+      <c r="A12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="15">
         <v>11</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>28</v>
+      <c r="G12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1229,7 +1256,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="3"/>
       <c r="H13" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8">

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E328F8-72C8-482B-9A1C-47BAFF00C5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCB35EE-12FF-4854-A0BE-DA0968993D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="33">
   <si>
     <t>StoryID</t>
   </si>
@@ -82,10 +71,6 @@
   </si>
   <si>
     <t>李东壁</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…..........</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -123,10 +108,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>爹，我看了好几遍了，确实没有我的名字…...</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -406,6 +387,22 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>老爷，我看了好几遍了，确实没有少爷的名字…...</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>老爷，少爷，榜上没找到少爷的名字。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <t>李</t>
     </r>
@@ -457,28 +454,30 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>科举的李东壁便下定决心开始随父亲学医。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-    <phoneticPr fontId="2"/>
+      <t>科举的李东壁决定开始随父亲学医。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/autumn.png</t>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/autumn_night.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +491,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -532,8 +531,15 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,12 +549,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,11 +580,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -595,15 +592,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -612,36 +618,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -919,365 +901,367 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="139.75" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="8.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="139.73046875" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="10">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="10">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C8" s="10">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="10">
+        <v>9</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="10">
+        <v>10</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="10">
+        <v>11</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="18" customFormat="1">
-      <c r="A5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="15">
-        <v>4</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="18" customFormat="1">
-      <c r="A8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="15">
-        <v>7</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="18" customFormat="1">
-      <c r="A10" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="15">
-        <v>9</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="18" customFormat="1">
-      <c r="A12" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="15">
-        <v>11</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="8"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCB35EE-12FF-4854-A0BE-DA0968993D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F59066-717F-432B-B1D5-71174DAA0E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -463,10 +474,11 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>res://Assets/Background/clinic/autumn_night.png</t>
+  </si>
+  <si>
     <t>res://Assets/Background/clinic/autumn.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/clinic/autumn_night.png</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -491,7 +503,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -533,7 +545,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -623,7 +635,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -904,15 +916,15 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="139.73046875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="139.75" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -962,7 +974,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>20</v>
@@ -1064,7 +1076,7 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>26</v>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F59066-717F-432B-B1D5-71174DAA0E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D8617-6508-4D83-BD14-59D104A74C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t>StoryID</t>
   </si>
@@ -474,10 +474,19 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/autumn_night.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/clinic/autumn.png</t>
+    <r>
+      <t>res://Assets/Background/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>001/001</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -592,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -632,6 +641,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,7 +935,7 @@
     <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="139.75" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
@@ -974,7 +986,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>20</v>
@@ -996,8 +1008,8 @@
       <c r="E3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>27</v>
+      <c r="F3" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1047,7 +1059,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1071,13 +1083,11 @@
       <c r="E6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>27</v>
+      <c r="F6" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="12" t="s">
         <v>26</v>
       </c>
@@ -1124,7 +1134,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1174,7 +1184,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1224,7 +1234,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93D8617-6508-4D83-BD14-59D104A74C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8D6120-C3E9-4DBF-8F9F-6135AB08001C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2753" yWindow="2813" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -486,6 +475,16 @@
         <charset val="134"/>
       </rPr>
       <t>001/001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.png</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -498,7 +497,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +511,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -554,7 +553,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -647,7 +646,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -928,15 +927,15 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="139.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="139.73046875" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8D6120-C3E9-4DBF-8F9F-6135AB08001C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0147F3AF-33F3-4DFB-BEAE-3F4D24F70F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2753" yWindow="2813" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -70,10 +81,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李东壁</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李言闻</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -487,6 +494,9 @@
       <t>.png</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧</t>
   </si>
 </sst>
 </file>
@@ -497,7 +507,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -511,7 +521,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -553,7 +563,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -646,7 +656,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -927,15 +937,15 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="139.73046875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="139.75" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -959,10 +969,10 @@
         <v>10</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>4</v>
@@ -985,10 +995,10 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1005,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>12</v>
@@ -1013,7 +1023,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1030,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -1038,7 +1048,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1055,15 +1065,15 @@
         <v>6</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1080,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>12</v>
@@ -1088,7 +1098,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1105,7 +1115,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>11</v>
@@ -1113,7 +1123,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1130,15 +1140,15 @@
         <v>6</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1155,7 +1165,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
@@ -1163,7 +1173,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1180,15 +1190,15 @@
         <v>6</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1205,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>11</v>
@@ -1213,7 +1223,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1230,15 +1240,15 @@
         <v>6</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1259,7 +1269,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0147F3AF-33F3-4DFB-BEAE-3F4D24F70F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF11EB-FBDC-440E-8845-CA5C32EB9697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20145" yWindow="4065" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -410,62 +410,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>李</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>壁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>十四岁考中秀才，可之后九年三次乡试落榜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，本就无心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>科举的李东壁决定开始随父亲学医。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -497,6 +441,42 @@
   </si>
   <si>
     <t>李东璧</t>
+  </si>
+  <si>
+    <r>
+      <t>李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东璧十四岁考中秀才，可之后九年三次乡试落榜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，本就无心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>科举的李东壁决定开始随父亲学医。</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -972,7 +952,7 @@
         <v>18</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>4</v>
@@ -995,7 +975,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>19</v>
@@ -1040,7 +1020,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>11</v>
@@ -1115,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>11</v>
@@ -1165,7 +1145,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>11</v>
@@ -1215,7 +1195,7 @@
         <v>6</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>11</v>
@@ -1269,7 +1249,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF11EB-FBDC-440E-8845-CA5C32EB9697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D500BB-D955-4CE8-93D0-86F5E2A296CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20145" yWindow="4065" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>StoryID</t>
   </si>
@@ -476,6 +476,14 @@
       </rPr>
       <t>科举的李东壁决定开始随父亲学医。</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -914,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="3" bestFit="1" customWidth="1"/>
@@ -924,12 +932,13 @@
     <col min="5" max="5" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="139.75" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="139.75" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -951,14 +960,17 @@
       <c r="G1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
@@ -974,14 +986,15 @@
       <c r="E2" s="10"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1001,12 +1014,15 @@
         <v>12</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1027,11 +1043,12 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="1"/>
+      <c r="J4" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
@@ -1052,11 +1069,12 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -1077,11 +1095,12 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="1"/>
+      <c r="J6" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
@@ -1102,11 +1121,12 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="1"/>
+      <c r="J7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1127,11 +1147,12 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="1"/>
+      <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
@@ -1152,11 +1173,12 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -1177,11 +1199,12 @@
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
@@ -1202,11 +1225,12 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="8" t="s">
         <v>8</v>
       </c>
@@ -1227,11 +1251,12 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="1"/>
+      <c r="J12" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="8" t="s">
         <v>8</v>
       </c>
@@ -1248,11 +1273,12 @@
       <c r="F13" s="1"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="2"/>
+      <c r="J13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
@@ -1261,9 +1287,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="I14" s="2"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
@@ -1272,7 +1299,8 @@
       <c r="F15" s="1"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAEA31B-DA23-4606-A25B-B16FF2B7A1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30396BC-8FB3-45CE-A484-D7C3C6D3D96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>StoryID</t>
   </si>
@@ -212,10 +223,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>老爷，少爷，榜上没找到少爷的名字。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -514,6 +521,10 @@
   </si>
   <si>
     <t>scene_enter</t>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -524,7 +535,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -538,7 +549,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -559,7 +570,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -690,7 +701,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -969,23 +980,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -1031,7 +1042,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>27</v>
@@ -1055,14 +1066,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="12"/>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="12"/>
     </row>
   </sheetData>
@@ -1076,14 +1087,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1145,12 +1156,12 @@
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>33</v>
+      <c r="F3" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1167,10 +1178,12 @@
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1181,16 +1194,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1207,10 +1222,12 @@
         <v>10</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1227,10 +1244,12 @@
         <v>9</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1241,16 +1260,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="F8" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1267,10 +1288,12 @@
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1281,16 +1304,18 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="F10" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1307,13 +1332,15 @@
         <v>9</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1321,16 +1348,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1346,7 +1375,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30396BC-8FB3-45CE-A484-D7C3C6D3D96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2011E269-D0C3-4755-9DCB-515674B4E37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
   <si>
     <t>StoryID</t>
   </si>
@@ -525,17 +514,20 @@
   <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -549,7 +541,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -570,7 +562,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -593,6 +585,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -679,8 +679,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -699,9 +697,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -979,24 +979,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1009,32 +1010,35 @@
       <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="17" t="s">
         <v>21</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -1056,25 +1060,26 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1087,14 +1092,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1149,7 +1154,7 @@
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -1160,7 +1165,7 @@
         <v>46</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1204,7 +1209,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1215,7 +1220,7 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -1226,7 +1231,7 @@
         <v>46</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="15" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1248,7 +1253,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1270,7 +1275,7 @@
         <v>46</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1292,7 +1297,7 @@
         <v>46</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1314,7 +1319,7 @@
         <v>46</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1336,11 +1341,11 @@
         <v>46</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="33">
+    <row r="12" spans="1:8" ht="30">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>46</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1374,7 +1379,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="14" t="s">
         <v>44</v>
       </c>
     </row>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2011E269-D0C3-4755-9DCB-515674B4E37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B82E4B9-5AEA-4FB2-8442-47D3E146E1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
   <si>
     <t>StoryID</t>
   </si>
@@ -517,6 +528,10 @@
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -527,7 +542,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -541,7 +556,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -562,7 +577,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -650,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -699,9 +714,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -979,25 +997,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:14">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1017,28 +1036,31 @@
         <v>18</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -1057,29 +1079,78 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:14">
       <c r="C3" s="10"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="1:13" ht="18">
+      <c r="G3" s="18"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" ht="18">
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5" s="10"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="7:7">
+      <c r="G20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1092,14 +1163,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1345,7 +1416,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30">
+    <row r="12" spans="1:8" ht="33">
       <c r="A12" s="1">
         <v>11</v>
       </c>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B82E4B9-5AEA-4FB2-8442-47D3E146E1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0878C5-ACEC-4C2E-A1E0-6A8A0EB6873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1000,20 +1000,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0878C5-ACEC-4C2E-A1E0-6A8A0EB6873D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDC0B59-0D66-42ED-B374-B68DC627FFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
   <si>
     <t>StoryID</t>
   </si>
@@ -531,6 +531,10 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -612,7 +616,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +638,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -665,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -715,6 +725,12 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -997,25 +1013,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1028,38 +1045,41 @@
       <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -1072,84 +1092,85 @@
       <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="C3" s="10"/>
-      <c r="G3" s="18"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="H3" s="18"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="C4" s="10"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="C5" s="10"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDC0B59-0D66-42ED-B374-B68DC627FFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C488E135-2291-40CF-85BE-C1C2D074FA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
   <si>
     <t>StoryID</t>
   </si>
@@ -98,12 +87,6 @@
   </si>
   <si>
     <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
   </si>
   <si>
     <t>NpcID</t>
@@ -536,6 +519,22 @@
   <si>
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -546,7 +545,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -560,7 +559,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -581,7 +580,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -735,7 +734,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1013,26 +1012,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1046,54 +1047,60 @@
         <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="K1" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="O1" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="20" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1107,57 +1114,59 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">
@@ -1183,14 +1192,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1232,10 +1241,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1246,18 +1255,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1268,18 +1277,18 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1290,18 +1299,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1312,18 +1321,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1334,18 +1343,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1356,18 +1365,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1378,18 +1387,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1400,18 +1409,18 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1422,21 +1431,21 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="33">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1444,18 +1453,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1471,7 +1480,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C488E135-2291-40CF-85BE-C1C2D074FA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAA017A-1D9C-4EBC-9439-F78353ACE716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>StoryID</t>
   </si>
@@ -514,10 +525,6 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -545,7 +552,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -559,7 +566,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -580,7 +587,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -734,7 +741,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1012,28 +1019,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1053,13 +1059,13 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>46</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
@@ -1067,26 +1073,23 @@
       <c r="K1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>47</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>49</v>
+      <c r="O1" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -1115,58 +1118,57 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">
@@ -1192,14 +1194,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1445,7 +1447,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30">
+    <row r="12" spans="1:8" ht="33">
       <c r="A12" s="1">
         <v>11</v>
       </c>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAA017A-1D9C-4EBC-9439-F78353ACE716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1333ADB4-C001-4DF1-BA49-4EF26AF827EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -103,10 +92,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -542,6 +527,10 @@
   <si>
     <t>TriggerEntryId</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -552,7 +541,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -566,7 +555,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -587,7 +576,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -741,7 +730,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1020,23 +1009,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1053,57 +1042,57 @@
         <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>20</v>
-      </c>
       <c r="P1" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1194,14 +1183,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1243,10 +1232,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1257,18 +1246,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1279,18 +1268,18 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1301,18 +1290,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1323,18 +1312,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1345,18 +1334,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1367,18 +1356,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1389,18 +1378,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1411,18 +1400,18 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1433,21 +1422,21 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="33">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1455,18 +1444,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1482,7 +1471,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1333ADB4-C001-4DF1-BA49-4EF26AF827EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31786492-5FDF-4793-B550-D257F5100D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -1097,9 +1097,7 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31786492-5FDF-4793-B550-D257F5100D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156349E2-AC22-4152-AD56-888F13F71D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>StoryID</t>
   </si>
@@ -214,55 +225,39 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>你再仔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>细</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>看看</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>老爷，我看了好几遍了，确实没有少爷的名字…...</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
-      <t>考了三次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>都没中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
+      <t>我看我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>是跟您学医吧，科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>举</t>
@@ -275,145 +270,6 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，看来我不是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>读书</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的材料啊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>爹</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的是什么</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，你看隔壁村那个老范</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>考了一辈子童试，年过半百中了秀才举人，你这才哪到哪</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>我看我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>是跟您学医吧，科</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>举</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
       <t>八股什么的，</t>
     </r>
     <r>
@@ -439,71 +295,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>学医哪里比得上做官有前途啊，你爹我行医一辈子，辛苦不赚钱不说，医得不好了还要受人白眼</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>可我真心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>喜欢研究那些药材方子，考证典籍。行医治病才是儿子此生志愿。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>......也罢，科举考功名的学子千千万，可真能博取个功名的又有几人呢。东壁呀，你若真的想从医，今日起便随为父从《内经》，《本草》学起吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>李</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东璧十四岁考中秀才，可之后九年三次乡试落榜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，本就无心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>科举的李东壁决定开始随父亲学医。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>scene_enter</t>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
@@ -531,17 +323,446 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你再仔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>细</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>看看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>辈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>子，辛苦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>又赚不到钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，医得不好了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>要受人白眼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>考了三次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都没中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，爹，看来我不是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的材料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的是什么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，你看隔壁村那个老范</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考了大半辈子童试，年过半百才中了秀才，后来又中了举人，你这才哪儿到哪儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>可我真心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜欢研究那些药材方子，考证典籍，不赚钱我也愿意干。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>......也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>考功名的学子千千万，可真能博取个功名的又有几人呢？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东璧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>呀，你若真的想从医，今日起便随</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>父从《内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>》、《本草》学起吧。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东璧十四岁考中秀才，可之后九年间三次参加乡试均告落榜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，本就无心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>科举的李东璧决定开始随父亲学医。</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -555,7 +776,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -576,7 +797,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -592,13 +813,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -670,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -708,17 +922,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -730,7 +938,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1009,26 +1217,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1044,41 +1252,41 @@
       <c r="E1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="G1" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="20" t="s">
+      <c r="K1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -1086,7 +1294,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>24</v>
@@ -1112,63 +1320,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
-      <c r="H3" s="18"/>
+      <c r="H3" s="16"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10"/>
-      <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="8:8">
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="8:8">
-      <c r="H20" s="18"/>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H14" s="16"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H15" s="16"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1179,20 +1387,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1218,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1232,11 +1440,11 @@
       <c r="G2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1250,15 +1458,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1272,15 +1478,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1294,15 +1498,13 @@
         <v>12</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1316,15 +1518,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1338,15 +1538,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1360,15 +1558,13 @@
         <v>12</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F8" s="8"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1382,15 +1578,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1404,15 +1598,13 @@
         <v>12</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1426,15 +1618,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30">
+      <c r="H11" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="36" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1448,15 +1638,13 @@
         <v>12</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="8" t="s">
-        <v>43</v>
-      </c>
+      <c r="F12" s="8"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1468,8 +1656,8 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="14" t="s">
-        <v>41</v>
+      <c r="H13" s="13" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156349E2-AC22-4152-AD56-888F13F71D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B45F9-DE73-4660-952B-E0FE2132DAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="2670" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -213,19 +202,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>老爷，少爷，榜上没找到少爷的名字。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>嘶...... 又没中......</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>李言闻</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>老爷，我看了好几遍了，确实没有少爷的名字…...</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -326,7 +307,271 @@
   </si>
   <si>
     <r>
-      <t>你再仔</t>
+      <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>辈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>子，辛苦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>又赚不到钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，医得不好了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>要受人白眼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>可我真心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜欢研究那些药材方子，考证典籍，不赚钱我也愿意干。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>......也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>考功名的学子千千万，可真能博取个功名的又有几人呢？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东璧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>呀，你若真的想从医，今日起便随</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>父从《内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>》、《本草》学起吧。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，榜上没找到少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的名字。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>你们再仔</t>
     </r>
     <r>
       <rPr>
@@ -362,87 +607,166 @@
   </si>
   <si>
     <r>
-      <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>辈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>子，辛苦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>又赚不到钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>不</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，医得不好了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>要受人白眼</t>
+      <t>考了三次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都没中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，爹，看来我不是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的材料...</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>我看了好几遍了，确</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没有少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的名字...</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的是什么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，你看隔壁村那个老范</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考了大半辈子童试，年过半百才中秀才，后来又中了举人，你这才哪儿到哪儿</t>
     </r>
     <r>
       <rPr>
@@ -458,267 +782,6 @@
   </si>
   <si>
     <r>
-      <t>考了三次</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>都没中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>举</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，爹，看来我不是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>读书</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的材料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的是什么</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>话</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，你看隔壁村那个老范</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>考了大半辈子童试，年过半百才中了秀才，后来又中了举人，你这才哪儿到哪儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>可我真心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>喜欢研究那些药材方子，考证典籍，不赚钱我也愿意干。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>......也</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>罢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，科</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>举</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>考功名的学子千千万，可真能博取个功名的又有几人呢？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东璧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>呀，你若真的想从医，今日起便随</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>父从《内</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>经</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>》、《本草》学起吧。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>李</t>
     </r>
     <r>
@@ -749,7 +812,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>科举的李东璧决定开始随父亲学医。</t>
+      <t>科举的李东璧决定开始随父亲学医</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -758,11 +821,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -776,7 +839,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -797,7 +860,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -821,6 +884,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -938,7 +1008,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1217,26 +1287,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1256,28 +1326,28 @@
         <v>17</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L1" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>38</v>
-      </c>
       <c r="N1" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>19</v>
@@ -1286,7 +1356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -1294,7 +1364,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>24</v>
@@ -1320,62 +1390,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="16"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="16"/>
     </row>
   </sheetData>
@@ -1387,20 +1457,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1426,7 +1496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1444,7 +1514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1461,10 +1531,10 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1481,10 +1551,10 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1492,7 +1562,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -1501,10 +1571,10 @@
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1521,10 +1591,10 @@
       <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1541,10 +1611,10 @@
       <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="36" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="36">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1552,7 +1622,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>12</v>
@@ -1561,10 +1631,10 @@
       <c r="F8" s="8"/>
       <c r="G8" s="2"/>
       <c r="H8" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1581,10 +1651,10 @@
       <c r="F9" s="8"/>
       <c r="G9" s="2"/>
       <c r="H9" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1592,7 +1662,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>12</v>
@@ -1601,10 +1671,10 @@
       <c r="F10" s="8"/>
       <c r="G10" s="2"/>
       <c r="H10" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1621,10 +1691,10 @@
       <c r="F11" s="8"/>
       <c r="G11" s="2"/>
       <c r="H11" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="36" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="36">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1632,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
@@ -1641,10 +1711,10 @@
       <c r="F12" s="8"/>
       <c r="G12" s="2"/>
       <c r="H12" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3">
         <v>12</v>
       </c>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771B45F9-DE73-4660-952B-E0FE2132DAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE901DE1-1B40-4299-BC55-51C4DF2E53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="2670" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -825,7 +836,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -839,7 +850,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -860,7 +871,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1008,7 +1019,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1287,23 +1298,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1356,7 +1367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -1395,54 +1406,54 @@
       <c r="H3" s="16"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="8:8">
@@ -1459,14 +1470,14 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE901DE1-1B40-4299-BC55-51C4DF2E53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD220F8-9143-451C-8629-9BD3632DD392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="53">
   <si>
     <t>LineIndex</t>
   </si>
@@ -87,28 +73,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
@@ -287,36 +254,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>scene_enter</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
     </r>
@@ -826,17 +763,102 @@
       <t>科举的李东璧决定开始随父亲学医</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -850,7 +872,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -871,7 +893,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -891,22 +913,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -921,20 +957,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -965,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -979,9 +1017,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -991,9 +1026,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1006,20 +1038,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1297,170 +1349,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="20" customFormat="1">
+      <c r="A1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="20" customFormat="1">
+      <c r="A2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="15" t="s">
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="M2" s="21"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="16"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="16"/>
+      <c r="T2" s="22"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="12"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="12"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="16"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="16"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="16"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="16"/>
+      <c r="H20" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{2A8A22AD-191D-4D99-BC1B-FF68A6520E80}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{22BAD810-6515-4B72-AA0B-214D5A9A1958}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{3EB00DCF-D275-45F7-A677-EC0CD61BBD76}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{14DAE2DF-14D1-41FB-B611-618EAA6C9D11}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{1B80E6D1-5516-443A-A86F-64B193185E55}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1470,41 +1551,41 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1512,17 +1593,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1530,19 +1611,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="13" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1550,19 +1631,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="13" t="s">
-        <v>30</v>
+      <c r="H4" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1570,19 +1651,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="13" t="s">
-        <v>45</v>
+      <c r="H5" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1590,19 +1671,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="8"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="13" t="s">
-        <v>47</v>
+      <c r="H6" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1610,19 +1691,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="8"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="13" t="s">
-        <v>46</v>
+      <c r="H7" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="36">
@@ -1630,19 +1711,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="8"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="13" t="s">
-        <v>48</v>
+      <c r="H8" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1650,19 +1731,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="13" t="s">
-        <v>32</v>
+      <c r="H9" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1670,19 +1751,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="8"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="13" t="s">
-        <v>41</v>
+      <c r="H10" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1690,19 +1771,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="13" t="s">
-        <v>42</v>
+      <c r="H11" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="36">
@@ -1710,19 +1791,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="13" t="s">
-        <v>43</v>
+      <c r="H12" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1730,15 +1811,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="13" t="s">
-        <v>49</v>
+      <c r="H13" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD220F8-9143-451C-8629-9BD3632DD392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894E488E-274E-4F77-BE7A-D31F9353FEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20085" yWindow="5055" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
   <si>
     <t>LineIndex</t>
   </si>
@@ -847,6 +858,10 @@
   </si>
   <si>
     <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -858,7 +873,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -872,7 +887,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -893,7 +908,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1003,7 +1018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1069,9 +1084,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1350,26 +1368,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="13" t="s">
         <v>35</v>
       </c>
@@ -1431,7 +1449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="21" t="s">
         <v>15</v>
       </c>
@@ -1548,21 +1566,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1587,8 +1605,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1605,8 +1626,9 @@
       <c r="H2" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1625,8 +1647,9 @@
       <c r="H3" s="11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1645,8 +1668,9 @@
       <c r="H4" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1665,8 +1689,9 @@
       <c r="H5" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1685,8 +1710,9 @@
       <c r="H6" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1705,8 +1731,9 @@
       <c r="H7" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="36">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="36">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1725,8 +1752,9 @@
       <c r="H8" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1745,8 +1773,9 @@
       <c r="H9" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1765,8 +1794,9 @@
       <c r="H10" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1785,8 +1815,9 @@
       <c r="H11" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="36">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="36">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1805,8 +1836,9 @@
       <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1821,6 +1853,7 @@
       <c r="H13" s="11" t="s">
         <v>34</v>
       </c>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/001落榜.xlsx
+++ b/DataTables/DetailText/剧情/001落榜.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894E488E-274E-4F77-BE7A-D31F9353FEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C6AA69-B71D-4E2B-90AE-50402A37D57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20085" yWindow="5055" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -266,102 +266,6 @@
   </si>
   <si>
     <r>
-      <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>辈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>子，辛苦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>又赚不到钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>不</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，医得不好了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>要受人白眼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>可我真心</t>
     </r>
     <r>
@@ -863,6 +767,102 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>学医哪里比得上做官有前途啊，你爹我行医一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>辈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>子，辛苦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>又赚不到钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，医得不好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>要受人白眼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1389,58 +1389,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="N1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="Q1" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="R1" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="R1" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="S1" s="19" t="s">
         <v>13</v>
@@ -1606,7 +1606,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1645,7 +1645,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="F5" s="7"/>
       <c r="G5" s="2"/>
       <c r="H5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1708,7 +1708,7 @@
       <c r="F6" s="7"/>
       <c r="G6" s="2"/>
       <c r="H6" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="F7" s="7"/>
       <c r="G7" s="2"/>
       <c r="H7" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -1750,7 +1750,7 @@
       <c r="F8" s="7"/>
       <c r="G8" s="2"/>
       <c r="H8" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -1792,7 +1792,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="2"/>
       <c r="H10" s="11" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -1813,7 +1813,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="2"/>
       <c r="H11" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -1834,7 +1834,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="2"/>
       <c r="H12" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -1851,7 +1851,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3"/>
     </row>
